--- a/data/processed/measles_bangladesh_consolidated.xlsx
+++ b/data/processed/measles_bangladesh_consolidated.xlsx
@@ -3572,7 +3572,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-11T17:41:59</t>
+          <t>2026-04-14T07:44:36</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/processed/measles_bangladesh_consolidated.xlsx
+++ b/data/processed/measles_bangladesh_consolidated.xlsx
@@ -3572,7 +3572,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-14T07:44:36</t>
+          <t>2026-04-15T07:44:27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/processed/measles_bangladesh_consolidated.xlsx
+++ b/data/processed/measles_bangladesh_consolidated.xlsx
@@ -3572,7 +3572,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-15T07:44:27</t>
+          <t>2026-04-16T07:45:25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/processed/measles_bangladesh_consolidated.xlsx
+++ b/data/processed/measles_bangladesh_consolidated.xlsx
@@ -3572,7 +3572,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-16T07:45:25</t>
+          <t>2026-04-17T07:45:34</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/processed/measles_bangladesh_consolidated.xlsx
+++ b/data/processed/measles_bangladesh_consolidated.xlsx
@@ -3572,7 +3572,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-17T07:45:34</t>
+          <t>2026-04-20T08:06:09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/processed/measles_bangladesh_consolidated.xlsx
+++ b/data/processed/measles_bangladesh_consolidated.xlsx
@@ -3572,7 +3572,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-20T08:06:09</t>
+          <t>2026-04-21T07:49:13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/processed/measles_bangladesh_consolidated.xlsx
+++ b/data/processed/measles_bangladesh_consolidated.xlsx
@@ -3572,7 +3572,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-21T07:49:13</t>
+          <t>2026-04-22T07:45:48</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/processed/measles_bangladesh_consolidated.xlsx
+++ b/data/processed/measles_bangladesh_consolidated.xlsx
@@ -13,7 +13,8 @@
     <sheet name="outbreak_2026_summary" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="outbreak_2026_divisions" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="outbreak_2026_districts" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="update_log" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="outbreak_2026_timeseries" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="update_log" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1624,7 +1625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1663,7 +1664,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1675,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12320</v>
+        <v>27164</v>
       </c>
     </row>
     <row r="5">
@@ -1684,7 +1685,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2241</v>
+        <v>3934</v>
       </c>
     </row>
     <row r="6">
@@ -1694,88 +1695,108 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6883</v>
+        <v>17998</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Deaths</t>
+          <t>Suspected deaths</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>166</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CFR (% of suspected)</t>
+          <t>Confirmed deaths</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>% deaths in 0-5 yr</t>
+          <t>Total deaths (susp+conf)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>% deaths in 5-18 yr</t>
+          <t>CFR (% of suspected)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>% deaths in adults</t>
+          <t>% deaths in 0-5 yr</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>% deaths in children (0-18)</t>
+          <t>% deaths in 5-18 yr</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>92.86</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Districts affected</t>
+          <t>% deaths in adults</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>61</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>% deaths in children (0-18)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>92.86</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Districts affected</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>DGHS / Hospital sentinel surveillance</t>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BSS News 2026-04-22 (auto)</t>
         </is>
       </c>
     </row>
@@ -3514,6 +3535,249 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Suspected_Cases</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Confirmed_Cases</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Hospitalised</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Suspected_Deaths</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Confirmed_Deaths</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Districts_Affected</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Total_Deaths</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>CFR_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>12320</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2241</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6883</v>
+      </c>
+      <c r="F2" t="n">
+        <v>166</v>
+      </c>
+      <c r="G2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>DGHS/HEOC hospital sentinel surveillance</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>166</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>18219</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2897</v>
+      </c>
+      <c r="E3" t="n">
+        <v>164</v>
+      </c>
+      <c r="F3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G3" t="n">
+        <v>58</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>WHO SEARO situation report</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>194</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>21467</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3192</v>
+      </c>
+      <c r="E4" t="n">
+        <v>174</v>
+      </c>
+      <c r="F4" t="n">
+        <v>37</v>
+      </c>
+      <c r="G4" t="n">
+        <v>58</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>BSS News / DGHS daily briefing</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>211</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>25935</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3805</v>
+      </c>
+      <c r="E5" t="n">
+        <v>188</v>
+      </c>
+      <c r="F5" t="n">
+        <v>38</v>
+      </c>
+      <c r="G5" t="n">
+        <v>58</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>The Daily Star / DGHS daily briefing</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>226</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>27164</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3934</v>
+      </c>
+      <c r="D6" t="n">
+        <v>17998</v>
+      </c>
+      <c r="E6" t="n">
+        <v>190</v>
+      </c>
+      <c r="F6" t="n">
+        <v>38</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>BSS News 2026-04-22 (auto)</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>228</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3572,7 +3836,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-22T07:45:48</t>
+          <t>2026-04-22T14:35:01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/processed/measles_bangladesh_consolidated.xlsx
+++ b/data/processed/measles_bangladesh_consolidated.xlsx
@@ -3836,7 +3836,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-22T14:35:01</t>
+          <t>2026-04-23T06:28:27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/processed/measles_bangladesh_consolidated.xlsx
+++ b/data/processed/measles_bangladesh_consolidated.xlsx
@@ -3836,7 +3836,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-23T06:28:27</t>
+          <t>2026-04-24T06:29:51</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/processed/measles_bangladesh_consolidated.xlsx
+++ b/data/processed/measles_bangladesh_consolidated.xlsx
@@ -3836,7 +3836,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-24T06:29:51</t>
+          <t>2026-04-27T07:21:50</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/processed/measles_bangladesh_consolidated.xlsx
+++ b/data/processed/measles_bangladesh_consolidated.xlsx
@@ -3836,7 +3836,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-27T07:21:50</t>
+          <t>2026-04-28T07:17:57</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/processed/measles_bangladesh_consolidated.xlsx
+++ b/data/processed/measles_bangladesh_consolidated.xlsx
@@ -3836,7 +3836,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-28T07:17:57</t>
+          <t>2026-04-29T07:10:17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/processed/measles_bangladesh_consolidated.xlsx
+++ b/data/processed/measles_bangladesh_consolidated.xlsx
@@ -3836,7 +3836,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-29T07:10:17</t>
+          <t>2026-04-30T07:15:02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/processed/measles_bangladesh_consolidated.xlsx
+++ b/data/processed/measles_bangladesh_consolidated.xlsx
@@ -3836,7 +3836,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-30T07:15:02</t>
+          <t>2026-05-01T07:17:37</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/processed/measles_bangladesh_consolidated.xlsx
+++ b/data/processed/measles_bangladesh_consolidated.xlsx
@@ -3836,7 +3836,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-01T07:17:37</t>
+          <t>2026-05-04T07:39:49</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/processed/measles_bangladesh_consolidated.xlsx
+++ b/data/processed/measles_bangladesh_consolidated.xlsx
@@ -3836,7 +3836,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04T07:39:49</t>
+          <t>2026-05-05T07:05:39</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/processed/measles_bangladesh_consolidated.xlsx
+++ b/data/processed/measles_bangladesh_consolidated.xlsx
@@ -3866,7 +3866,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-06T07:22:55</t>
+          <t>2026-05-07T07:32:48</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/processed/measles_bangladesh_consolidated.xlsx
+++ b/data/processed/measles_bangladesh_consolidated.xlsx
@@ -3866,7 +3866,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-07T07:32:48</t>
+          <t>2026-05-08T06:21:23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/processed/measles_bangladesh_consolidated.xlsx
+++ b/data/processed/measles_bangladesh_consolidated.xlsx
@@ -3866,7 +3866,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-08T06:21:23</t>
+          <t>2026-05-11T08:06:04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/processed/measles_bangladesh_consolidated.xlsx
+++ b/data/processed/measles_bangladesh_consolidated.xlsx
@@ -3866,7 +3866,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-11T08:06:04</t>
+          <t>2026-05-12T07:31:42</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
